--- a/lead_generation_forms/023_kitchen_remodeling_lead_generation_form--lead_generation_forms.xlsx
+++ b/lead_generation_forms/023_kitchen_remodeling_lead_generation_form--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lead Location Other</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -794,7 +794,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Budget Other</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -840,7 +840,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Preferred Contact Method Other</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lead Source Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -927,12 +927,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>lead_source_other</t>
+          <t>lead_source_other_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lead Source Other 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Follow Up Method Other</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
